--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Infrastructure ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Infrastructure ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="119">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Infrastructure ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -112,6 +112,30 @@
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
   </si>
   <si>
@@ -121,28 +145,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
+    <t>MAX Healthcare Institute Ltd</t>
+  </si>
+  <si>
+    <t>INE027H01010</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
   </si>
   <si>
     <t>Apollo Hospitals Enterprise Ltd.</t>
@@ -151,9 +160,6 @@
     <t>INE437A01024</t>
   </si>
   <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
     <t>The Indian Hotels Company Ltd.</t>
   </si>
   <si>
@@ -169,124 +175,124 @@
     <t>INE245A01021</t>
   </si>
   <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>DLF Ltd.</t>
+  </si>
+  <si>
+    <t>INE271C01023</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE129A01019</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Indus Towers Ltd.</t>
+  </si>
+  <si>
+    <t>INE121J01017</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>CG Power and Industrial Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE067A01029</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Shree Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE070A01015</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Godrej Properties Ltd.</t>
+  </si>
+  <si>
+    <t>INE484J01027</t>
+  </si>
+  <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>Adani Green Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE364U01010</t>
+  </si>
+  <si>
     <t>Siemens Ltd.</t>
   </si>
   <si>
     <t>INE003A01024</t>
   </si>
   <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>DLF Ltd.</t>
-  </si>
-  <si>
-    <t>INE271C01023</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Indus Towers Ltd.</t>
-  </si>
-  <si>
-    <t>INE121J01017</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Godrej Properties Ltd.</t>
-  </si>
-  <si>
-    <t>INE484J01027</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
-    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE335Y01020</t>
-  </si>
-  <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
-    <t>Container Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE111A01025</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -334,19 +340,25 @@
     <t>Net Current Assets</t>
   </si>
   <si>
+    <t>^</t>
+  </si>
+  <si>
     <t>Total Net Assets</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -629,10 +641,10 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -729,13 +741,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -753,8 +765,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15697200"/>
-          <a:ext cx="3686175" cy="1905000"/>
+          <a:off x="666750" y="16078200"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -768,13 +780,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -792,8 +804,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18554700"/>
-          <a:ext cx="3686175" cy="1905000"/>
+          <a:off x="666750" y="18935700"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1126,11 +1138,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J94"/>
+  <dimension ref="B1:J96"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="55.285714285714285" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="50.285714285714285" collapsed="true"/>
@@ -1226,10 +1238,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>11522.590000000002</v>
+        <v>15399.860000000004</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9993062841239999</v>
+        <v>0.9989503518585999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1263,10 +1275,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>11522.590000000002</v>
+        <v>15399.860000000004</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9993062841239999</v>
+        <v>0.9989503518585999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1289,13 +1301,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>193504</v>
+        <v>226659</v>
       </c>
       <c r="G8" s="15">
-        <v>2448.02</v>
+        <v>3220.60</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2123065881598</v>
+        <v>0.208912256553</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1318,13 +1330,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>98085</v>
+        <v>119558</v>
       </c>
       <c r="G9" s="15">
-        <v>1595.16</v>
+        <v>2219.24</v>
       </c>
       <c r="H9" s="16">
-        <v>0.13834158919</v>
+        <v>0.1439565410894</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1347,13 +1359,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>43052</v>
+        <v>52294</v>
       </c>
       <c r="G10" s="15">
-        <v>1535.84</v>
+        <v>1921.86</v>
       </c>
       <c r="H10" s="16">
-        <v>0.1331970124261</v>
+        <v>0.1246662452272</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1376,13 +1388,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>173186</v>
+        <v>211338</v>
       </c>
       <c r="G11" s="15">
-        <v>561.12</v>
+        <v>705.66</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0486636027272</v>
+        <v>0.0457743969941</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1405,13 +1417,13 @@
         <v>26</v>
       </c>
       <c r="F12" s="14">
-        <v>165665</v>
+        <v>202001</v>
       </c>
       <c r="G12" s="15">
-        <v>499.73</v>
+        <v>585.3</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0433395034767</v>
+        <v>0.0379669452153</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1434,13 +1446,13 @@
         <v>31</v>
       </c>
       <c r="F13" s="14">
-        <v>4170</v>
+        <v>5169</v>
       </c>
       <c r="G13" s="15">
-        <v>479.03</v>
+        <v>579.44</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0415442786113</v>
+        <v>0.0375868216907</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1463,13 +1475,13 @@
         <v>34</v>
       </c>
       <c r="F14" s="14">
-        <v>141864</v>
+        <v>32965</v>
       </c>
       <c r="G14" s="15">
-        <v>372.55</v>
+        <v>472.32</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0323097112846</v>
+        <v>0.0306382155545</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1489,16 +1501,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F15" s="14">
-        <v>13590</v>
+        <v>8727</v>
       </c>
       <c r="G15" s="15">
-        <v>340.95</v>
+        <v>465.15</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0295691747751</v>
+        <v>0.0301731156106</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1509,25 +1521,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F16" s="14">
-        <v>7173</v>
+        <v>17106</v>
       </c>
       <c r="G16" s="15">
-        <v>310.19</v>
+        <v>435.48</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0269014879704</v>
+        <v>0.0282484970141</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1550,13 +1562,13 @@
         <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>26957</v>
+        <v>173222</v>
       </c>
       <c r="G17" s="15">
-        <v>296.35</v>
+        <v>414.69</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0257012023599</v>
+        <v>0.0268999017791</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1579,13 +1591,13 @@
         <v>45</v>
       </c>
       <c r="F18" s="14">
-        <v>3702</v>
+        <v>33198</v>
       </c>
       <c r="G18" s="15">
-        <v>252.12</v>
+        <v>373.54</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0218653185051</v>
+        <v>0.0242306043323</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1605,16 +1617,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F19" s="14">
-        <v>32152</v>
+        <v>4500</v>
       </c>
       <c r="G19" s="15">
-        <v>245.87</v>
+        <v>309.62</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0213232820119</v>
+        <v>0.0200842740091</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1625,25 +1637,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F20" s="14">
-        <v>61737</v>
+        <v>39214</v>
       </c>
       <c r="G20" s="15">
-        <v>225.03</v>
+        <v>301.89</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0195159155291</v>
+        <v>0.0195828482676</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1663,16 +1675,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F21" s="14">
-        <v>3228</v>
+        <v>74922</v>
       </c>
       <c r="G21" s="15">
-        <v>196.05</v>
+        <v>294.29</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0170026007176</v>
+        <v>0.0190898553005</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1683,10 +1695,10 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
@@ -1695,13 +1707,13 @@
         <v>17</v>
       </c>
       <c r="F22" s="14">
-        <v>70788</v>
+        <v>86467</v>
       </c>
       <c r="G22" s="15">
-        <v>184.83</v>
+        <v>275.31</v>
       </c>
       <c r="H22" s="16">
-        <v>0.016029536805</v>
+        <v>0.0178586702327</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1712,10 +1724,10 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>13</v>
@@ -1724,13 +1736,13 @@
         <v>17</v>
       </c>
       <c r="F23" s="14">
-        <v>137009</v>
+        <v>165941</v>
       </c>
       <c r="G23" s="15">
-        <v>176.04</v>
+        <v>235.59</v>
       </c>
       <c r="H23" s="16">
-        <v>0.015267216681</v>
+        <v>0.0152821333047</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1741,25 +1753,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>60</v>
-      </c>
       <c r="F24" s="14">
-        <v>98768</v>
+        <v>28654</v>
       </c>
       <c r="G24" s="15">
-        <v>174.94</v>
+        <v>228.62</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0151718182582</v>
+        <v>0.0148300068599</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1770,25 +1782,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="F25" s="14">
-        <v>23435</v>
+        <v>120308</v>
       </c>
       <c r="G25" s="15">
-        <v>174.60</v>
+        <v>228.34</v>
       </c>
       <c r="H25" s="16">
-        <v>0.015142331473</v>
+        <v>0.0148118439611</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1799,10 +1811,10 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
@@ -1811,13 +1823,13 @@
         <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>45391</v>
+        <v>58979</v>
       </c>
       <c r="G26" s="15">
-        <v>157.60</v>
+        <v>226.57</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0136679922116</v>
+        <v>0.0146970284938</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1828,25 +1840,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>68</v>
-      </c>
       <c r="F27" s="14">
-        <v>107809</v>
+        <v>131496</v>
       </c>
       <c r="G27" s="15">
-        <v>152.29</v>
+        <v>201.35</v>
       </c>
       <c r="H27" s="16">
-        <v>0.013207478007</v>
+        <v>0.013061070253</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1857,25 +1869,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="D28" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="F28" s="14">
-        <v>4951</v>
+        <v>6027</v>
       </c>
       <c r="G28" s="15">
-        <v>144.27</v>
+        <v>196.97</v>
       </c>
       <c r="H28" s="16">
-        <v>0.012511936779</v>
+        <v>0.012776950622</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1886,25 +1898,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="F29" s="14">
-        <v>491</v>
+        <v>28614</v>
       </c>
       <c r="G29" s="15">
-        <v>136.48</v>
+        <v>196.49</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0118363424939</v>
+        <v>0.012745814224</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1924,16 +1936,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="F30" s="14">
-        <v>5509</v>
+        <v>42881</v>
       </c>
       <c r="G30" s="15">
-        <v>128.33</v>
+        <v>176.26</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0111295269068</v>
+        <v>0.0114335447866</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1956,13 +1968,13 @@
         <v>31</v>
       </c>
       <c r="F31" s="14">
-        <v>24541</v>
+        <v>581</v>
       </c>
       <c r="G31" s="15">
-        <v>125.85</v>
+        <v>171.95</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0109144468263</v>
+        <v>0.0111539658803</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1982,16 +1994,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F32" s="14">
-        <v>35084</v>
+        <v>29754</v>
       </c>
       <c r="G32" s="15">
-        <v>125.69</v>
+        <v>164.69</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0109005706921</v>
+        <v>0.0106830278618</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2011,16 +2023,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F33" s="14">
-        <v>9560</v>
+        <v>6723</v>
       </c>
       <c r="G33" s="15">
-        <v>117.02</v>
+        <v>150.85</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0101486576688</v>
+        <v>0.0097852617217</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2043,13 +2055,13 @@
         <v>84</v>
       </c>
       <c r="F34" s="14">
-        <v>52318</v>
+        <v>63829</v>
       </c>
       <c r="G34" s="15">
-        <v>113.44</v>
+        <v>150.66</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0098381791655</v>
+        <v>0.0097729368975</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2069,16 +2081,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F35" s="14">
-        <v>11016</v>
+        <v>11943</v>
       </c>
       <c r="G35" s="15">
-        <v>90.58</v>
+        <v>148.2</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0078556264881</v>
+        <v>0.0096133628582</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2098,16 +2110,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="F36" s="14">
-        <v>74</v>
+        <v>13729</v>
       </c>
       <c r="G36" s="15">
-        <v>84.09</v>
+        <v>139.26</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0072927757936</v>
+        <v>0.0090334474469</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2127,16 +2139,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F37" s="14">
-        <v>10067</v>
+        <v>3929</v>
       </c>
       <c r="G37" s="15">
-        <v>78.53</v>
+        <v>128.31</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0068105801293</v>
+        <v>0.0083231483693</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2147,6 +2159,27 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" s="14">
+        <v>3283</v>
+      </c>
+      <c r="G38" s="15">
+        <v>81.36</v>
+      </c>
+      <c r="H38" s="16">
+        <v>0.0052776194476</v>
+      </c>
+      <c r="I38" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="11" t="s">
@@ -2154,28 +2187,7 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I39" s="9" t="s">
+      <c r="B39" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
@@ -2183,7 +2195,28 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="11" t="s">
@@ -2191,28 +2224,7 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I41" s="9" t="s">
+      <c r="B41" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
@@ -2220,7 +2232,28 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J42" s="11" t="s">
@@ -2228,36 +2261,36 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="12" t="s">
+      <c r="C44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J44" s="11" t="s">
@@ -2265,36 +2298,36 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="12" t="s">
+      <c r="H46" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J46" s="11" t="s">
@@ -2302,28 +2335,7 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I47" s="9" t="s">
+      <c r="B47" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="11" t="s">
@@ -2331,7 +2343,28 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I48" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J48" s="11" t="s">
@@ -2339,28 +2372,7 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I49" s="9" t="s">
+      <c r="B49" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -2368,7 +2380,28 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I50" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -2376,28 +2409,7 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I51" s="9" t="s">
+      <c r="B51" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J51" s="11" t="s">
@@ -2405,7 +2417,28 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J52" s="11" t="s">
@@ -2413,28 +2446,7 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I53" s="9" t="s">
+      <c r="B53" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J53" s="11" t="s">
@@ -2442,7 +2454,28 @@
       </c>
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I54" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J54" s="11" t="s">
@@ -2450,28 +2483,7 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I55" s="9" t="s">
+      <c r="B55" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J55" s="11" t="s">
@@ -2479,7 +2491,28 @@
       </c>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J56" s="11" t="s">
@@ -2487,28 +2520,7 @@
       </c>
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I57" s="9" t="s">
+      <c r="B57" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J57" s="11" t="s">
@@ -2516,7 +2528,28 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J58" s="11" t="s">
@@ -2524,28 +2557,7 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I59" s="9" t="s">
+      <c r="B59" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J59" s="11" t="s">
@@ -2553,7 +2565,28 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J60" s="11" t="s">
@@ -2561,28 +2594,7 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I61" s="9" t="s">
+      <c r="B61" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J61" s="11" t="s">
@@ -2590,7 +2602,28 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I62" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J62" s="11" t="s">
@@ -2598,28 +2631,7 @@
       </c>
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I63" s="9" t="s">
+      <c r="B63" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J63" s="11" t="s">
@@ -2627,7 +2639,28 @@
       </c>
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I64" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J64" s="11" t="s">
@@ -2635,28 +2668,7 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="9">
-        <v>2.46</v>
-      </c>
-      <c r="H65" s="10">
-        <v>0.0002133455637</v>
-      </c>
-      <c r="I65" s="9" t="s">
+      <c r="B65" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="11" t="s">
@@ -2664,7 +2676,28 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="9">
+        <v>16.66</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0.0010806924778</v>
+      </c>
+      <c r="I66" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="11" t="s">
@@ -2672,37 +2705,16 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="18">
-        <v>5.538952599992626</v>
-      </c>
-      <c r="H67" s="19">
-        <v>0.0004803703108975768</v>
-      </c>
-      <c r="I67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="20" t="s">
+      <c r="B67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>13</v>
@@ -2717,33 +2729,50 @@
         <v>13</v>
       </c>
       <c r="G68" s="18">
-        <v>11530.5889526</v>
-      </c>
-      <c r="H68" s="19">
-        <v>0.9999999999985977</v>
+        <v>-0.4785808000033285</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J68" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" ht="15" customHeight="1">
-      <c r="B71" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-    </row>
-    <row r="72" spans="2:8" ht="15" customHeight="1">
+      <c r="J68" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15" customHeight="1">
+      <c r="B69" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="18">
+        <v>15416.0414192</v>
+      </c>
+      <c r="H69" s="20">
+        <v>0.9999999999984283</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" ht="15" customHeight="1">
       <c r="B72" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -2751,10 +2780,11 @@
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
-    </row>
-    <row r="73" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B73" s="22" t="s">
-        <v>109</v>
+      <c r="I72" s="21"/>
+    </row>
+    <row r="73" spans="2:8" ht="15" customHeight="1">
+      <c r="B73" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -2763,9 +2793,9 @@
       <c r="G73" s="21"/>
       <c r="H73" s="21"/>
     </row>
-    <row r="74" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B74" s="22" t="s">
-        <v>110</v>
+    <row r="74" spans="2:8" ht="15" customHeight="1">
+      <c r="B74" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
@@ -2776,7 +2806,7 @@
     </row>
     <row r="75" spans="2:8" ht="27.6" customHeight="1">
       <c r="B75" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -2785,31 +2815,54 @@
       <c r="G75" s="21"/>
       <c r="H75" s="21"/>
     </row>
-    <row r="78" ht="15">
-      <c r="B78" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" ht="15">
-      <c r="B93" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="94" ht="15">
-      <c r="B94" s="21" t="s">
+    <row r="76" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B76" s="22" t="s">
         <v>114</v>
       </c>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+    </row>
+    <row r="77" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B77" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+    </row>
+    <row r="80" ht="15">
+      <c r="B80" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="95" ht="15">
+      <c r="B95" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="96" ht="15">
+      <c r="B96" s="21" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B73:H73"/>
+  <mergeCells count="9">
     <mergeCell ref="B74:H74"/>
     <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B77:H77"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B71:I71"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B73:H73"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
